--- a/outputs/per-fund/vc-investments-electric-capital.xlsx
+++ b/outputs/per-fund/vc-investments-electric-capital.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Electric Capital. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Electric Capital. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -16659,11 +16659,11 @@
         <v>1</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, polychain</t>
+          <t>blockchain-capital, coinfund, digital-currency-group, electric-capital, polychain</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -16785,11 +16785,11 @@
         <v>1</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, dragonfly, electric-capital, pantera, polychain</t>
+          <t>a16z-crypto, dragonfly, electric-capital, pantera, polychain, yzi-labs</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -16848,11 +16848,11 @@
         <v>1</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, electric-capital, paradigm, polychain</t>
+          <t>1kx, arrington-capital, coinbase-ventures, dragonfly, electric-capital, paradigm, polychain</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -16911,11 +16911,11 @@
         <v>0</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, electric-capital, pantera</t>
+          <t>arrington-capital, dragonfly, electric-capital, hashed, huobi-ventures, pantera</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -16974,11 +16974,11 @@
         <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, maven11</t>
+          <t>electric-capital, maven11, yzi-labs</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -17096,11 +17096,11 @@
         <v>0</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, polychain</t>
+          <t>cms-holdings, coinbase-ventures, electric-capital, polychain</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -17285,11 +17285,11 @@
         <v>1</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, framework-ventures, robot-ventures</t>
+          <t>coinbase-ventures, digital-currency-group, electric-capital, framework-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
@@ -17348,11 +17348,11 @@
         <v>0</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, multicoin-capital</t>
+          <t>cms-holdings, electric-capital, multicoin-capital</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -17533,11 +17533,11 @@
         <v>2</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>1kx, electric-capital, galaxy-digital, hypersphere, parafi-capital</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -17655,11 +17655,11 @@
         <v>1</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, electric-capital, robot-ventures</t>
+          <t>alliance-dao, coinfund, delphi-ventures, electric-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -17781,11 +17781,11 @@
         <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>electric-capital, okx-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -17903,11 +17903,11 @@
         <v>1</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, lemniscap, polychain</t>
+          <t>cms-holdings, coinbase-ventures, electric-capital, lemniscap, polychain</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -17962,11 +17962,11 @@
         <v>0</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>1kx, electric-capital</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -18027,11 +18027,11 @@
         <v>2</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, electric-capital</t>
+          <t>alameda-research, arrington-capital, dragonfly, electric-capital, galaxy-digital</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -18090,11 +18090,11 @@
         <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, framework-ventures, lemniscap, semantic-ventures</t>
+          <t>coinbase-ventures, coinfund, electric-capital, framework-ventures, hypersphere, lemniscap, semantic-ventures</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -18153,11 +18153,11 @@
         <v>1</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, delphi-ventures, electric-capital, paradigm, polychain</t>
+          <t>a16z-crypto, cms-holdings, cmt-digital, delphi-ventures, electric-capital, hashkey-capital, paradigm, polychain</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -18216,11 +18216,11 @@
         <v>1</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, framework-ventures, gnosis-vc</t>
+          <t>electric-capital, framework-ventures, gnosis-vc, parafi-capital</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -18275,11 +18275,11 @@
         <v>1</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, polychain, robot-ventures</t>
+          <t>alliance-dao, electric-capital, iosg-ventures, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -18338,11 +18338,11 @@
         <v>1</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, maven11</t>
+          <t>1kx, alliance-dao, blockchain-capital, digital-currency-group, electric-capital, gsr, maven11, spartan-group</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -18464,11 +18464,11 @@
         <v>0</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, electric-capital</t>
+          <t>a16z-crypto, coinbase-ventures, coinfund, electric-capital</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -18523,11 +18523,11 @@
         <v>1</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, electric-capital</t>
+          <t>digital-currency-group, dragonfly, electric-capital, sfermion, spartan-group</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -18712,11 +18712,11 @@
         <v>0</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>electric-capital, mirana-ventures, parafi-capital</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -18834,11 +18834,11 @@
         <v>2</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>electric-capital, galaxy-digital</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -19023,11 +19023,11 @@
         <v>2</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital</t>
+          <t>alameda-research, coinbase-ventures, electric-capital</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -19210,11 +19210,11 @@
         <v>2</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, electric-capital</t>
+          <t>animoca-brands, coinbase-ventures, dragonfly, electric-capital, parafi-capital, spartan-group</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -19273,11 +19273,11 @@
         <v>1</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, electric-capital</t>
+          <t>a16z-crypto, arrington-capital, electric-capital, sequoia-capital</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -19336,11 +19336,11 @@
         <v>2</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital</t>
+          <t>coinbase-ventures, electric-capital, hashed</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -19399,11 +19399,11 @@
         <v>1</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, electric-capital</t>
+          <t>a16z-crypto, coinbase-ventures, electric-capital, hack-vc</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -19462,11 +19462,11 @@
         <v>1</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>alameda-research, amber-group, electric-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -19588,11 +19588,11 @@
         <v>2</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, multicoin-capital</t>
+          <t>alameda-research, electric-capital, multicoin-capital, sequoia-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -19714,11 +19714,11 @@
         <v>0</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>alameda-research, alliance-dao, cmt-digital, coinfund, electric-capital</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -19777,11 +19777,11 @@
         <v>3</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>electric-capital, gsr, hypersphere</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -19840,11 +19840,11 @@
         <v>3</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>electric-capital, hypersphere</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
@@ -19903,11 +19903,11 @@
         <v>0</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>blockchain-capital, electric-capital, sequoia-capital</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -20029,11 +20029,11 @@
         <v>1</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, electric-capital, lemniscap</t>
+          <t>dragonfly, electric-capital, jump-crypto, lemniscap</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -20092,11 +20092,11 @@
         <v>1</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>electric-capital, sfermion</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -20155,11 +20155,11 @@
         <v>0</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>alameda-research, electric-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -20216,11 +20216,11 @@
         <v>2</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>electric-capital, sequoia-capital</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -20342,11 +20342,11 @@
         <v>2</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, framework-ventures</t>
+          <t>electric-capital, framework-ventures, gsr</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -20405,11 +20405,11 @@
         <v>2</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>alliance-dao, electric-capital, polygon-ventures</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -20468,11 +20468,11 @@
         <v>0</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, framework-ventures, lemniscap</t>
+          <t>coinbase-ventures, coinfund, electric-capital, framework-ventures, galaxy-digital, jump-crypto, lemniscap</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -20531,11 +20531,11 @@
         <v>2</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, polychain</t>
+          <t>electric-capital, hypersphere, polychain</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -20594,11 +20594,11 @@
         <v>0</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, paradigm</t>
+          <t>electric-capital, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
@@ -20659,11 +20659,11 @@
         <v>0</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, electric-capital</t>
+          <t>coinbase-ventures, dragonfly, electric-capital, gsr, jump-crypto</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -20718,11 +20718,11 @@
         <v>0</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>electric-capital, gsr, okx-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -20781,11 +20781,11 @@
         <v>0</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>coinfund, electric-capital, longhash-ventures</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
@@ -20903,11 +20903,11 @@
         <v>0</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, framework-ventures</t>
+          <t>electric-capital, framework-ventures, polygon-ventures</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
@@ -21151,11 +21151,11 @@
         <v>1</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, pantera</t>
+          <t>alameda-research, digital-currency-group, electric-capital, jump-crypto, pantera</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
@@ -21214,11 +21214,11 @@
         <v>0</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>electric-capital, parafi-capital</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
@@ -21277,11 +21277,11 @@
         <v>1</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, robot-ventures</t>
+          <t>circle-ventures, coinbase-ventures, electric-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr">
@@ -21342,11 +21342,11 @@
         <v>1</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, polychain</t>
+          <t>blockchain-capital, coinbase-ventures, electric-capital, hack-vc, polychain</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
@@ -21468,11 +21468,11 @@
         <v>1</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital</t>
+          <t>circle-ventures, coinbase-ventures, electric-capital, hack-vc</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
@@ -21527,11 +21527,11 @@
         <v>1</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, electric-capital</t>
+          <t>delphi-ventures, electric-capital, mh-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M80" s="7" t="inlineStr">
@@ -21653,11 +21653,11 @@
         <v>0</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, framework-ventures</t>
+          <t>electric-capital, framework-ventures, gsr, jump-crypto</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr">
@@ -21779,11 +21779,11 @@
         <v>2</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>electric-capital, mh-ventures</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
@@ -21962,11 +21962,11 @@
         <v>0</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>arrington-capital, electric-capital</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
@@ -22025,11 +22025,11 @@
         <v>0</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>arrington-capital, electric-capital</t>
         </is>
       </c>
       <c r="M88" s="7" t="inlineStr">
@@ -22147,11 +22147,11 @@
         <v>0</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, robot-ventures</t>
+          <t>electric-capital, mirana-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M90" s="7" t="inlineStr">
@@ -22399,11 +22399,11 @@
         <v>2</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, lemniscap</t>
+          <t>animoca-brands, coinbase-ventures, electric-capital, gsr, lemniscap, mechanism-capital</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
@@ -22769,11 +22769,11 @@
         <v>2</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>amber-group, electric-capital, parafi-capital</t>
         </is>
       </c>
       <c r="M100" s="7" t="inlineStr">
@@ -22887,11 +22887,11 @@
         <v>1</v>
       </c>
       <c r="K102" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>alliance-dao, electric-capital</t>
         </is>
       </c>
       <c r="M102" s="7" t="inlineStr">
@@ -23013,11 +23013,11 @@
         <v>1</v>
       </c>
       <c r="K104" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>cms-holdings, electric-capital</t>
         </is>
       </c>
       <c r="M104" s="7" t="inlineStr">
@@ -23072,11 +23072,11 @@
         <v>3</v>
       </c>
       <c r="K105" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, robot-ventures</t>
+          <t>electric-capital, hashed, mirana-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M105" s="7" t="inlineStr">
@@ -23194,11 +23194,11 @@
         <v>0</v>
       </c>
       <c r="K107" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, haun-ventures</t>
+          <t>electric-capital, haun-ventures, parafi-capital</t>
         </is>
       </c>
       <c r="M107" s="7" t="inlineStr">
@@ -23314,11 +23314,11 @@
         <v>0</v>
       </c>
       <c r="K109" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>arrington-capital, electric-capital</t>
         </is>
       </c>
       <c r="M109" s="7" t="inlineStr">
@@ -23560,11 +23560,11 @@
         <v>1</v>
       </c>
       <c r="K113" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, maven11, pantera</t>
+          <t>arrington-capital, big-brain-holdings, borderless-capital, electric-capital, galaxy-digital, gsr, maven11, pantera, parafi-capital</t>
         </is>
       </c>
       <c r="M113" s="7" t="inlineStr">
@@ -23745,11 +23745,11 @@
         <v>1</v>
       </c>
       <c r="K116" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>amber-group, electric-capital</t>
         </is>
       </c>
       <c r="M116" s="7" t="inlineStr">
@@ -23808,11 +23808,11 @@
         <v>1</v>
       </c>
       <c r="K117" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>electric-capital</t>
+          <t>amber-group, electric-capital, gsr</t>
         </is>
       </c>
       <c r="M117" s="7" t="inlineStr">
@@ -29146,7 +29146,7 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n"/>
@@ -29158,7 +29158,7 @@
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -29166,7 +29166,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
